--- a/output/pdf_financials_xlsx/AVN.xlsx
+++ b/output/pdf_financials_xlsx/AVN.xlsx
@@ -5550,10 +5550,10 @@
         <v>-0.012667</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.06854399999999999</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.051667</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>0.030731</v>
@@ -5697,10 +5697,10 @@
         <v>-0.013707</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.015761</v>
+        <v>0.052783</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.059179</v>
+        <v>0.110846</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0.030731</v>
@@ -6282,43 +6282,43 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.144483</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.191345</v>
+        <v>0.145479</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.08498799999999999</v>
+        <v>-0.052655</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.058458</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.372388</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.1313</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>4.765876</v>
+        <v>4.568292</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-5.135891</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-15.907111</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.488811</v>
+        <v>-1.437203</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.099874</v>
+        <v>0.032805</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.613544</v>
+        <v>0.375091</v>
       </c>
     </row>
     <row r="119">
@@ -13646,7 +13646,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -14252,7 +14256,11 @@
           <t>Prepaids and deposits (Note 11)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -14772,7 +14780,11 @@
           <t>Prepaids and deposits 10</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -18340,7 +18352,11 @@
           <t>Exploration and evaluation asset expenditures 6</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -20790,7 +20806,11 @@
           <t>Exploration and evaluation asset expenditures 8, 11</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -22216,7 +22236,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -27980,7 +28004,11 @@
           <t>Sales tax and other receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -29444,7 +29472,11 @@
           <t>Accounts receivable, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -29870,7 +29902,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -31768,7 +31804,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -34198,7 +34238,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AVN.xlsx
+++ b/output/pdf_financials_xlsx/AVN.xlsx
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.027581</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.012978</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.006784</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1815,13 +1815,13 @@
         <v>-0.320794</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.55857</v>
+        <v>-10.586151</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.294086</v>
+        <v>-8.307064</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-11.644652</v>
+        <v>-11.651436</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-4.46977</v>
@@ -1917,13 +1917,13 @@
         <v>-0.320794</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.55857</v>
+        <v>-10.586151</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.294086</v>
+        <v>-8.307064</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-11.644652</v>
+        <v>-11.651436</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-4.46977</v>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.168331</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.567145</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.2757</v>
@@ -2170,10 +2170,10 @@
         <v>0.585575</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.042286</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.439756</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.338611</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.168331</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.567145</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.2757</v>
@@ -2268,10 +2268,10 @@
         <v>0.585575</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.042286</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.439756</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.338611</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.168331</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.579812</v>
+        <v>0.012667</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.120712</v>
@@ -2856,10 +2856,10 @@
         <v>0.016435</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.06696100000000001</v>
+        <v>0.024675</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.451467</v>
+        <v>0.011711</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.10591</v>
@@ -6600,19 +6600,19 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.002282</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003733</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08907900000000001</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016743</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017468</v>
       </c>
     </row>
     <row r="125">
@@ -6649,19 +6649,19 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.002282</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003733</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08907900000000001</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016743</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017468</v>
       </c>
     </row>
     <row r="126">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -18204,7 +18204,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -20722,7 +20726,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -37106,7 +37114,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -37192,7 +37200,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -43568,11 +43576,7 @@
           <t>General and administrative fees (Note 8)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" s="5" t="n">
         <v>0.000674</v>
       </c>

--- a/output/pdf_financials_xlsx/AVN.xlsx
+++ b/output/pdf_financials_xlsx/AVN.xlsx
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.0779</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.47257</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -18694,7 +18694,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -26642,7 +26646,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AVN.xlsx
+++ b/output/pdf_financials_xlsx/AVN.xlsx
@@ -23860,7 +23860,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31996,7 +32000,11 @@
           <t>Common shares issued for cash 7</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
